--- a/pokemon/source/new_entries.xlsx
+++ b/pokemon/source/new_entries.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="New entries" sheetId="1" state="visible" r:id="rId1"/>
@@ -426,7 +426,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C500"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>

--- a/pokemon/source/new_entries.xlsx
+++ b/pokemon/source/new_entries.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="New entries" sheetId="1" state="visible" r:id="rId1"/>

--- a/pokemon/source/new_entries.xlsx
+++ b/pokemon/source/new_entries.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C500"/>
+  <dimension ref="A1:C469"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2790,167 +2790,12 @@
       <c r="B469" s="2" t="n"/>
       <c r="C469" s="2" t="n"/>
     </row>
-    <row r="470">
-      <c r="A470" s="2" t="n"/>
-      <c r="B470" s="2" t="n"/>
-      <c r="C470" s="2" t="n"/>
-    </row>
-    <row r="471">
-      <c r="A471" s="2" t="n"/>
-      <c r="B471" s="2" t="n"/>
-      <c r="C471" s="2" t="n"/>
-    </row>
-    <row r="472">
-      <c r="A472" s="2" t="n"/>
-      <c r="B472" s="2" t="n"/>
-      <c r="C472" s="2" t="n"/>
-    </row>
-    <row r="473">
-      <c r="A473" s="2" t="n"/>
-      <c r="B473" s="2" t="n"/>
-      <c r="C473" s="2" t="n"/>
-    </row>
-    <row r="474">
-      <c r="A474" s="2" t="n"/>
-      <c r="B474" s="2" t="n"/>
-      <c r="C474" s="2" t="n"/>
-    </row>
-    <row r="475">
-      <c r="A475" s="2" t="n"/>
-      <c r="B475" s="2" t="n"/>
-      <c r="C475" s="2" t="n"/>
-    </row>
-    <row r="476">
-      <c r="A476" s="2" t="n"/>
-      <c r="B476" s="2" t="n"/>
-      <c r="C476" s="2" t="n"/>
-    </row>
-    <row r="477">
-      <c r="A477" s="2" t="n"/>
-      <c r="B477" s="2" t="n"/>
-      <c r="C477" s="2" t="n"/>
-    </row>
-    <row r="478">
-      <c r="A478" s="2" t="n"/>
-      <c r="B478" s="2" t="n"/>
-      <c r="C478" s="2" t="n"/>
-    </row>
-    <row r="479">
-      <c r="A479" s="2" t="n"/>
-      <c r="B479" s="2" t="n"/>
-      <c r="C479" s="2" t="n"/>
-    </row>
-    <row r="480">
-      <c r="A480" s="2" t="n"/>
-      <c r="B480" s="2" t="n"/>
-      <c r="C480" s="2" t="n"/>
-    </row>
-    <row r="481">
-      <c r="A481" s="2" t="n"/>
-      <c r="B481" s="2" t="n"/>
-      <c r="C481" s="2" t="n"/>
-    </row>
-    <row r="482">
-      <c r="A482" s="2" t="n"/>
-      <c r="B482" s="2" t="n"/>
-      <c r="C482" s="2" t="n"/>
-    </row>
-    <row r="483">
-      <c r="A483" s="2" t="n"/>
-      <c r="B483" s="2" t="n"/>
-      <c r="C483" s="2" t="n"/>
-    </row>
-    <row r="484">
-      <c r="A484" s="2" t="n"/>
-      <c r="B484" s="2" t="n"/>
-      <c r="C484" s="2" t="n"/>
-    </row>
-    <row r="485">
-      <c r="A485" s="2" t="n"/>
-      <c r="B485" s="2" t="n"/>
-      <c r="C485" s="2" t="n"/>
-    </row>
-    <row r="486">
-      <c r="A486" s="2" t="n"/>
-      <c r="B486" s="2" t="n"/>
-      <c r="C486" s="2" t="n"/>
-    </row>
-    <row r="487">
-      <c r="A487" s="2" t="n"/>
-      <c r="B487" s="2" t="n"/>
-      <c r="C487" s="2" t="n"/>
-    </row>
-    <row r="488">
-      <c r="A488" s="2" t="n"/>
-      <c r="B488" s="2" t="n"/>
-      <c r="C488" s="2" t="n"/>
-    </row>
-    <row r="489">
-      <c r="A489" s="2" t="n"/>
-      <c r="B489" s="2" t="n"/>
-      <c r="C489" s="2" t="n"/>
-    </row>
-    <row r="490">
-      <c r="A490" s="2" t="n"/>
-      <c r="B490" s="2" t="n"/>
-      <c r="C490" s="2" t="n"/>
-    </row>
-    <row r="491">
-      <c r="A491" s="2" t="n"/>
-      <c r="B491" s="2" t="n"/>
-      <c r="C491" s="2" t="n"/>
-    </row>
-    <row r="492">
-      <c r="A492" s="2" t="n"/>
-      <c r="B492" s="2" t="n"/>
-      <c r="C492" s="2" t="n"/>
-    </row>
-    <row r="493">
-      <c r="A493" s="2" t="n"/>
-      <c r="B493" s="2" t="n"/>
-      <c r="C493" s="2" t="n"/>
-    </row>
-    <row r="494">
-      <c r="A494" s="2" t="n"/>
-      <c r="B494" s="2" t="n"/>
-      <c r="C494" s="2" t="n"/>
-    </row>
-    <row r="495">
-      <c r="A495" s="2" t="n"/>
-      <c r="B495" s="2" t="n"/>
-      <c r="C495" s="2" t="n"/>
-    </row>
-    <row r="496">
-      <c r="A496" s="2" t="n"/>
-      <c r="B496" s="2" t="n"/>
-      <c r="C496" s="2" t="n"/>
-    </row>
-    <row r="497">
-      <c r="A497" s="2" t="n"/>
-      <c r="B497" s="2" t="n"/>
-      <c r="C497" s="2" t="n"/>
-    </row>
-    <row r="498">
-      <c r="A498" s="2" t="n"/>
-      <c r="B498" s="2" t="n"/>
-      <c r="C498" s="2" t="n"/>
-    </row>
-    <row r="499">
-      <c r="A499" s="2" t="n"/>
-      <c r="B499" s="2" t="n"/>
-      <c r="C499" s="2" t="n"/>
-    </row>
-    <row r="500">
-      <c r="A500" s="2" t="n"/>
-      <c r="B500" s="2" t="n"/>
-      <c r="C500" s="2" t="n"/>
-    </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B469" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"normal,holo,reverse,pokeball,masterball,friendball,loveball,quickball,duskball,energysymbol,rocket"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
+    <dataValidation sqref="C2:C469" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/pokemon/source/new_entries.xlsx
+++ b/pokemon/source/new_entries.xlsx
@@ -2793,7 +2793,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="B2:B469" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"normal,holo,reverse,pokeball,masterball,friendball,loveball,quickball,duskball,energysymbol,rocket"</formula1>
+      <formula1>"normal,holo,reverse,1st-normal,1st-holo,pokeball,masterball,friendball,loveball,quickball,duskball,energysymbol,rocket,cosmos,altholo,stamp,prerelease,staff,promo"</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C469" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="greaterThanOrEqual">
       <formula1>1</formula1>
